--- a/TEST - SP 2026 - predtekmovanje - rezultati.xlsx
+++ b/TEST - SP 2026 - predtekmovanje - rezultati.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{C23C4284-10F7-4640-AAD8-E2ABC3C7069E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -938,23 +938,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -974,6 +962,18 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1278,108 +1278,108 @@
       <c r="E1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="38"/>
       <c r="G1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="39"/>
+      <c r="H1" s="38"/>
       <c r="I1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="39"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="38"/>
       <c r="N1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="39"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="38"/>
       <c r="R1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="38"/>
-      <c r="T1" s="39"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="38"/>
       <c r="U1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="39"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="38"/>
       <c r="Z1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="38"/>
-      <c r="AB1" s="38"/>
-      <c r="AC1" s="39"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="38"/>
       <c r="AD1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="39"/>
+      <c r="AE1" s="40"/>
+      <c r="AF1" s="38"/>
       <c r="AG1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="AH1" s="38"/>
-      <c r="AI1" s="38"/>
-      <c r="AJ1" s="38"/>
-      <c r="AK1" s="39"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="38"/>
       <c r="AL1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AM1" s="38"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="39"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="38"/>
       <c r="AP1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="AQ1" s="38"/>
-      <c r="AR1" s="38"/>
-      <c r="AS1" s="39"/>
+      <c r="AQ1" s="40"/>
+      <c r="AR1" s="40"/>
+      <c r="AS1" s="38"/>
       <c r="AT1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="38"/>
-      <c r="AV1" s="38"/>
-      <c r="AW1" s="39"/>
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AW1" s="38"/>
       <c r="AX1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AY1" s="38"/>
-      <c r="AZ1" s="38"/>
-      <c r="BA1" s="39"/>
+      <c r="AY1" s="40"/>
+      <c r="AZ1" s="40"/>
+      <c r="BA1" s="38"/>
       <c r="BB1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="BC1" s="38"/>
-      <c r="BD1" s="38"/>
-      <c r="BE1" s="38"/>
-      <c r="BF1" s="38"/>
-      <c r="BG1" s="39"/>
+      <c r="BC1" s="40"/>
+      <c r="BD1" s="40"/>
+      <c r="BE1" s="40"/>
+      <c r="BF1" s="40"/>
+      <c r="BG1" s="38"/>
       <c r="BH1" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="BI1" s="38"/>
-      <c r="BJ1" s="38"/>
-      <c r="BK1" s="38"/>
-      <c r="BL1" s="38"/>
-      <c r="BM1" s="39"/>
+      <c r="BI1" s="40"/>
+      <c r="BJ1" s="40"/>
+      <c r="BK1" s="40"/>
+      <c r="BL1" s="40"/>
+      <c r="BM1" s="38"/>
       <c r="BN1" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="BO1" s="38"/>
-      <c r="BP1" s="38"/>
-      <c r="BQ1" s="38"/>
-      <c r="BR1" s="38"/>
-      <c r="BS1" s="39"/>
+      <c r="BO1" s="40"/>
+      <c r="BP1" s="40"/>
+      <c r="BQ1" s="40"/>
+      <c r="BR1" s="40"/>
+      <c r="BS1" s="38"/>
       <c r="BT1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="BU1" s="38"/>
-      <c r="BV1" s="38"/>
-      <c r="BW1" s="39"/>
+      <c r="BU1" s="40"/>
+      <c r="BV1" s="40"/>
+      <c r="BW1" s="38"/>
       <c r="BX1" s="9"/>
     </row>
     <row r="2" spans="1:123" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1608,78 +1608,78 @@
       <c r="BW2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BX2" s="40" t="s">
+      <c r="BX2" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="BY2" s="38"/>
-      <c r="BZ2" s="38"/>
-      <c r="CA2" s="39"/>
-      <c r="CB2" s="45" t="s">
+      <c r="BY2" s="40"/>
+      <c r="BZ2" s="40"/>
+      <c r="CA2" s="38"/>
+      <c r="CB2" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="CC2" s="38"/>
-      <c r="CD2" s="38"/>
-      <c r="CE2" s="39"/>
-      <c r="CF2" s="46" t="s">
+      <c r="CC2" s="40"/>
+      <c r="CD2" s="40"/>
+      <c r="CE2" s="38"/>
+      <c r="CF2" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="CG2" s="38"/>
-      <c r="CH2" s="38"/>
-      <c r="CI2" s="39"/>
-      <c r="CJ2" s="41" t="s">
+      <c r="CG2" s="40"/>
+      <c r="CH2" s="40"/>
+      <c r="CI2" s="38"/>
+      <c r="CJ2" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="CK2" s="38"/>
-      <c r="CL2" s="38"/>
-      <c r="CM2" s="39"/>
-      <c r="CN2" s="47" t="s">
+      <c r="CK2" s="40"/>
+      <c r="CL2" s="40"/>
+      <c r="CM2" s="38"/>
+      <c r="CN2" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="CO2" s="38"/>
-      <c r="CP2" s="38"/>
-      <c r="CQ2" s="39"/>
-      <c r="CR2" s="48" t="s">
+      <c r="CO2" s="40"/>
+      <c r="CP2" s="40"/>
+      <c r="CQ2" s="38"/>
+      <c r="CR2" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="CS2" s="38"/>
-      <c r="CT2" s="38"/>
-      <c r="CU2" s="39"/>
-      <c r="CV2" s="42" t="s">
+      <c r="CS2" s="40"/>
+      <c r="CT2" s="40"/>
+      <c r="CU2" s="38"/>
+      <c r="CV2" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="CW2" s="38"/>
-      <c r="CX2" s="38"/>
-      <c r="CY2" s="39"/>
-      <c r="CZ2" s="49" t="s">
+      <c r="CW2" s="40"/>
+      <c r="CX2" s="40"/>
+      <c r="CY2" s="38"/>
+      <c r="CZ2" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="DA2" s="38"/>
-      <c r="DB2" s="38"/>
-      <c r="DC2" s="39"/>
-      <c r="DD2" s="50" t="s">
+      <c r="DA2" s="40"/>
+      <c r="DB2" s="40"/>
+      <c r="DC2" s="38"/>
+      <c r="DD2" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="DE2" s="38"/>
-      <c r="DF2" s="38"/>
-      <c r="DG2" s="39"/>
-      <c r="DH2" s="43" t="s">
+      <c r="DE2" s="40"/>
+      <c r="DF2" s="40"/>
+      <c r="DG2" s="38"/>
+      <c r="DH2" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="DI2" s="38"/>
-      <c r="DJ2" s="38"/>
-      <c r="DK2" s="39"/>
-      <c r="DL2" s="51" t="s">
+      <c r="DI2" s="40"/>
+      <c r="DJ2" s="40"/>
+      <c r="DK2" s="38"/>
+      <c r="DL2" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="DM2" s="38"/>
-      <c r="DN2" s="38"/>
-      <c r="DO2" s="39"/>
-      <c r="DP2" s="44" t="s">
+      <c r="DM2" s="40"/>
+      <c r="DN2" s="40"/>
+      <c r="DO2" s="38"/>
+      <c r="DP2" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="DQ2" s="38"/>
-      <c r="DR2" s="38"/>
-      <c r="DS2" s="39"/>
+      <c r="DQ2" s="40"/>
+      <c r="DR2" s="40"/>
+      <c r="DS2" s="38"/>
     </row>
     <row r="3" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
@@ -2698,7 +2698,7 @@
       <c r="A10" s="35"/>
       <c r="B10" s="14"/>
       <c r="C10" s="30">
-        <f t="shared" ref="C4:C67" si="0">SUM(D10:DS10)</f>
+        <f t="shared" ref="C10:C67" si="0">SUM(D10:DS10)</f>
         <v>0</v>
       </c>
       <c r="D10" s="28"/>
@@ -39819,6 +39819,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="BX2:CA2"/>
+    <mergeCell ref="CJ2:CM2"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="BT1:BW1"/>
+    <mergeCell ref="AL1:AO1"/>
+    <mergeCell ref="CV2:CY2"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="BB1:BG1"/>
+    <mergeCell ref="DH2:DK2"/>
+    <mergeCell ref="BH1:BM1"/>
+    <mergeCell ref="BN1:BS1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="DP2:DS2"/>
     <mergeCell ref="AX1:BA1"/>
@@ -39835,19 +39848,6 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="CV2:CY2"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="BB1:BG1"/>
-    <mergeCell ref="DH2:DK2"/>
-    <mergeCell ref="BH1:BM1"/>
-    <mergeCell ref="BN1:BS1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="BX2:CA2"/>
-    <mergeCell ref="CJ2:CM2"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="BT1:BW1"/>
-    <mergeCell ref="AL1:AO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TEST - SP 2026 - predtekmovanje - rezultati.xlsx
+++ b/TEST - SP 2026 - predtekmovanje - rezultati.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\Documents\SP2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Moje\StaveSP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C23C4284-10F7-4640-AAD8-E2ABC3C7069E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12D9703D-FC6A-48E0-8BAF-9150830214E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>11.6.</t>
   </si>
@@ -347,6 +347,9 @@
     <t>L</t>
   </si>
   <si>
+    <t>K</t>
+  </si>
+  <si>
     <t>Gregor Bernik</t>
   </si>
   <si>
@@ -374,7 +377,10 @@
     <t>1.</t>
   </si>
   <si>
-    <t>3.</t>
+    <t>2.</t>
+  </si>
+  <si>
+    <t>4.</t>
   </si>
   <si>
     <t>6.</t>
@@ -383,7 +389,7 @@
     <t>7.</t>
   </si>
   <si>
-    <t>K</t>
+    <t>5.</t>
   </si>
 </sst>
 </file>
@@ -938,11 +944,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -962,18 +980,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1278,108 +1284,108 @@
       <c r="E1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="38"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="38"/>
+      <c r="H1" s="39"/>
       <c r="I1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="39"/>
       <c r="N1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="39"/>
       <c r="R1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="40"/>
-      <c r="T1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="39"/>
       <c r="U1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="39"/>
       <c r="Z1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="39"/>
       <c r="AD1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="AE1" s="40"/>
-      <c r="AF1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="39"/>
       <c r="AG1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
+      <c r="AK1" s="39"/>
       <c r="AL1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="40"/>
-      <c r="AO1" s="38"/>
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="39"/>
       <c r="AP1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="AQ1" s="40"/>
-      <c r="AR1" s="40"/>
-      <c r="AS1" s="38"/>
+      <c r="AQ1" s="38"/>
+      <c r="AR1" s="38"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="AU1" s="40"/>
-      <c r="AV1" s="40"/>
-      <c r="AW1" s="38"/>
+      <c r="AU1" s="38"/>
+      <c r="AV1" s="38"/>
+      <c r="AW1" s="39"/>
       <c r="AX1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AY1" s="40"/>
-      <c r="AZ1" s="40"/>
-      <c r="BA1" s="38"/>
+      <c r="AY1" s="38"/>
+      <c r="AZ1" s="38"/>
+      <c r="BA1" s="39"/>
       <c r="BB1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="BC1" s="40"/>
-      <c r="BD1" s="40"/>
-      <c r="BE1" s="40"/>
-      <c r="BF1" s="40"/>
-      <c r="BG1" s="38"/>
+      <c r="BC1" s="38"/>
+      <c r="BD1" s="38"/>
+      <c r="BE1" s="38"/>
+      <c r="BF1" s="38"/>
+      <c r="BG1" s="39"/>
       <c r="BH1" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="BI1" s="40"/>
-      <c r="BJ1" s="40"/>
-      <c r="BK1" s="40"/>
-      <c r="BL1" s="40"/>
-      <c r="BM1" s="38"/>
+      <c r="BI1" s="38"/>
+      <c r="BJ1" s="38"/>
+      <c r="BK1" s="38"/>
+      <c r="BL1" s="38"/>
+      <c r="BM1" s="39"/>
       <c r="BN1" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="BO1" s="40"/>
-      <c r="BP1" s="40"/>
-      <c r="BQ1" s="40"/>
-      <c r="BR1" s="40"/>
-      <c r="BS1" s="38"/>
+      <c r="BO1" s="38"/>
+      <c r="BP1" s="38"/>
+      <c r="BQ1" s="38"/>
+      <c r="BR1" s="38"/>
+      <c r="BS1" s="39"/>
       <c r="BT1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="BU1" s="40"/>
-      <c r="BV1" s="40"/>
-      <c r="BW1" s="38"/>
+      <c r="BU1" s="38"/>
+      <c r="BV1" s="38"/>
+      <c r="BW1" s="39"/>
       <c r="BX1" s="9"/>
     </row>
     <row r="2" spans="1:123" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1608,88 +1614,88 @@
       <c r="BW2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BX2" s="50" t="s">
+      <c r="BX2" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="BY2" s="40"/>
-      <c r="BZ2" s="40"/>
-      <c r="CA2" s="38"/>
-      <c r="CB2" s="41" t="s">
+      <c r="BY2" s="38"/>
+      <c r="BZ2" s="38"/>
+      <c r="CA2" s="39"/>
+      <c r="CB2" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="CC2" s="40"/>
-      <c r="CD2" s="40"/>
-      <c r="CE2" s="38"/>
-      <c r="CF2" s="42" t="s">
+      <c r="CC2" s="38"/>
+      <c r="CD2" s="38"/>
+      <c r="CE2" s="39"/>
+      <c r="CF2" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="CG2" s="40"/>
-      <c r="CH2" s="40"/>
-      <c r="CI2" s="38"/>
-      <c r="CJ2" s="51" t="s">
+      <c r="CG2" s="38"/>
+      <c r="CH2" s="38"/>
+      <c r="CI2" s="39"/>
+      <c r="CJ2" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="CK2" s="40"/>
-      <c r="CL2" s="40"/>
-      <c r="CM2" s="38"/>
-      <c r="CN2" s="43" t="s">
+      <c r="CK2" s="38"/>
+      <c r="CL2" s="38"/>
+      <c r="CM2" s="39"/>
+      <c r="CN2" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="CO2" s="40"/>
-      <c r="CP2" s="40"/>
-      <c r="CQ2" s="38"/>
-      <c r="CR2" s="44" t="s">
+      <c r="CO2" s="38"/>
+      <c r="CP2" s="38"/>
+      <c r="CQ2" s="39"/>
+      <c r="CR2" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="CS2" s="40"/>
-      <c r="CT2" s="40"/>
-      <c r="CU2" s="38"/>
-      <c r="CV2" s="48" t="s">
+      <c r="CS2" s="38"/>
+      <c r="CT2" s="38"/>
+      <c r="CU2" s="39"/>
+      <c r="CV2" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="CW2" s="40"/>
-      <c r="CX2" s="40"/>
-      <c r="CY2" s="38"/>
-      <c r="CZ2" s="45" t="s">
+      <c r="CW2" s="38"/>
+      <c r="CX2" s="38"/>
+      <c r="CY2" s="39"/>
+      <c r="CZ2" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="DA2" s="40"/>
-      <c r="DB2" s="40"/>
-      <c r="DC2" s="38"/>
-      <c r="DD2" s="46" t="s">
+      <c r="DA2" s="38"/>
+      <c r="DB2" s="38"/>
+      <c r="DC2" s="39"/>
+      <c r="DD2" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="DE2" s="40"/>
-      <c r="DF2" s="40"/>
-      <c r="DG2" s="38"/>
-      <c r="DH2" s="49" t="s">
+      <c r="DE2" s="38"/>
+      <c r="DF2" s="38"/>
+      <c r="DG2" s="39"/>
+      <c r="DH2" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="DI2" s="40"/>
-      <c r="DJ2" s="40"/>
-      <c r="DK2" s="38"/>
-      <c r="DL2" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="DM2" s="40"/>
-      <c r="DN2" s="40"/>
-      <c r="DO2" s="38"/>
-      <c r="DP2" s="39" t="s">
+      <c r="DI2" s="38"/>
+      <c r="DJ2" s="38"/>
+      <c r="DK2" s="39"/>
+      <c r="DL2" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="DM2" s="38"/>
+      <c r="DN2" s="38"/>
+      <c r="DO2" s="39"/>
+      <c r="DP2" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="DQ2" s="40"/>
-      <c r="DR2" s="40"/>
-      <c r="DS2" s="38"/>
+      <c r="DQ2" s="38"/>
+      <c r="DR2" s="38"/>
+      <c r="DS2" s="39"/>
     </row>
     <row r="3" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" s="26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="27">
         <v>1</v>
@@ -1700,12 +1706,8 @@
       <c r="F3" s="13">
         <v>0</v>
       </c>
-      <c r="G3" s="11">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
-        <v>1</v>
-      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="11"/>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
@@ -1832,13 +1834,13 @@
     </row>
     <row r="4" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C4" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="28">
         <v>3</v>
@@ -1849,12 +1851,8 @@
       <c r="F4" s="17">
         <v>1</v>
       </c>
-      <c r="G4" s="15">
-        <v>0</v>
-      </c>
-      <c r="H4" s="17">
-        <v>1</v>
-      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="15"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
@@ -1975,29 +1973,25 @@
     </row>
     <row r="5" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>108</v>
-      </c>
       <c r="C5" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="28">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
         <v>3</v>
       </c>
-      <c r="E5" s="15">
-        <v>0</v>
-      </c>
       <c r="F5" s="17">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
-      <c r="H5" s="17">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="17"/>
       <c r="I5" s="15"/>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
@@ -2120,29 +2114,25 @@
     </row>
     <row r="6" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="17">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
         <v>0</v>
       </c>
-      <c r="H6" s="17">
-        <v>1</v>
-      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="15"/>
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
@@ -2265,13 +2255,13 @@
     </row>
     <row r="7" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="28">
         <v>1</v>
@@ -2282,12 +2272,8 @@
       <c r="F7" s="17">
         <v>1</v>
       </c>
-      <c r="G7" s="15">
-        <v>0</v>
-      </c>
-      <c r="H7" s="17">
-        <v>1</v>
-      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="17"/>
       <c r="I7" s="15"/>
       <c r="J7" s="16"/>
       <c r="K7" s="16"/>
@@ -2410,13 +2396,13 @@
     </row>
     <row r="8" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="28">
         <v>3</v>
@@ -2427,12 +2413,8 @@
       <c r="F8" s="17">
         <v>0</v>
       </c>
-      <c r="G8" s="15">
-        <v>0</v>
-      </c>
-      <c r="H8" s="17">
-        <v>1</v>
-      </c>
+      <c r="G8" s="15"/>
+      <c r="H8" s="17"/>
       <c r="I8" s="15"/>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
@@ -2553,13 +2535,13 @@
     </row>
     <row r="9" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -2570,12 +2552,8 @@
       <c r="F9" s="17">
         <v>0</v>
       </c>
-      <c r="G9" s="15">
-        <v>0</v>
-      </c>
-      <c r="H9" s="17">
-        <v>1</v>
-      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="17"/>
       <c r="I9" s="15"/>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
@@ -39819,19 +39797,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="BX2:CA2"/>
-    <mergeCell ref="CJ2:CM2"/>
-    <mergeCell ref="AG1:AK1"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="BT1:BW1"/>
-    <mergeCell ref="AL1:AO1"/>
-    <mergeCell ref="CV2:CY2"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="BB1:BG1"/>
-    <mergeCell ref="DH2:DK2"/>
-    <mergeCell ref="BH1:BM1"/>
-    <mergeCell ref="BN1:BS1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="DP2:DS2"/>
     <mergeCell ref="AX1:BA1"/>
@@ -39848,6 +39813,19 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="N1:Q1"/>
     <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="CV2:CY2"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="BB1:BG1"/>
+    <mergeCell ref="DH2:DK2"/>
+    <mergeCell ref="BH1:BM1"/>
+    <mergeCell ref="BN1:BS1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="BX2:CA2"/>
+    <mergeCell ref="CJ2:CM2"/>
+    <mergeCell ref="AG1:AK1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="BT1:BW1"/>
+    <mergeCell ref="AL1:AO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
